--- a/bank_import_template/odoo19_bank_transaction_import_template.xlsx
+++ b/bank_import_template/odoo19_bank_transaction_import_template.xlsx
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -766,195 +766,227 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>STEP 1</t>
+          <t>IMPORTANT — use the RIGHT import path</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Delete sample rows 2–9 from the 'Bank Transactions' sheet. Keep Row 1 exactly as-is — Odoo uses it for column auto-mapping.</t>
+          <t>Do NOT use 'Accounting → Bank journal → Import'. That path runs the bank-statement file parser (CSV/OFX/CAMT/QIF) which only auto-links partners via IBAN — it ignores partner_id and leaves every line with 'Set Partner' / 'Set Account' buttons. Use Odoo's generic data import on the account.bank.statement.line model instead — see STEP 4.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>STEP 2</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Paste your real transactions from Row 2 downward.
-Date: YYYY-MM-DD  |  Amount: positive = credit (money in), negative = debit (money out)  |  payment_ref must be unique per row.</t>
-        </is>
-      </c>
+      <c r="A5" s="6" t="inlineStr"/>
+      <c r="B5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>STEP 3</t>
+          <t>STEP 1</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Save the file as Excel Workbook (.xlsx). Do not rename the sheet or change the field names in Row 1.</t>
+          <t>Delete sample rows 2–9 from the 'Bank Transactions' sheet. Keep Row 1 exactly as-is — Odoo uses it for column auto-mapping.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>STEP 4</t>
+          <t>STEP 2</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>In Odoo 19: Accounting → Bank journal → Import → choose this file.
-Enable 'Use first row as header'. Sheet: Bank Transactions.</t>
+          <t>Paste your real transactions from Row 2 downward.
+Date: YYYY-MM-DD  |  Amount: positive = credit (money in), negative = debit (money out)  |  payment_ref must be unique per row.
+Every partner_id value must match the display name of an existing res.partner in Odoo (case-sensitive). Create the partner first if it doesn't exist.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>STEP 5</t>
+          <t>STEP 3</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>All 6 columns auto-map. Click Test, then Import.
-Lines will appear in Bank Matching already linked to the partner and journal, so 'Reconcile' shows up directly (not 'Set Partner' / 'Set Account').</t>
+          <t>Save the file as Excel Workbook (.xlsx). Do not rename the sheet or change the field names in Row 1.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>STEP 4</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>In Odoo 19, enable Developer Mode (Settings → Developer Tools → Activate developer mode).
+Open this URL in the same browser tab — it loads the bank statement line list view:
+    /odoo/action-account.action_bank_statement_line
+Click the ⚙ (cog) / Actions menu → 'Import records' → upload this .xlsx → keep sheet 'Bank Transactions' and 'Use first row as headers' on.
+This path uses Odoo's base_import which DOES resolve Many2one fields like partner_id and journal_id by display name.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Field Reference</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr"/>
+          <t>STEP 5</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Click 'Test'. Every row should show resolved partner_id and journal_id (no 'partner Infosys Ltd not found' style warnings). Then click 'Import'.
+Open the Bank Matching widget — imported lines will already show partner + 'Reconcile' / 'Receivable', exactly like a manually-created line.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Transaction date. ISO format YYYY-MM-DD. Example: 2025-03-31.</t>
-        </is>
-      </c>
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>journal_id</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Bank journal name (e.g. 'Bank'). Must match an existing account.journal of type bank.</t>
-        </is>
-      </c>
+          <t>Field Reference</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>payment_ref</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Unique bank reference: UTR / NEFT / IMPS / UPI Ref ID / cheque number. Shown as the label on the statement line.</t>
+          <t>Transaction date. ISO format YYYY-MM-DD. Example: 2025-03-31.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>journal_id</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Signed amount. Positive (+) = money in (credit). Negative (−) = money out (debit).</t>
+          <t>Bank journal display name (e.g. 'Bank'). base_import resolves it by name_search; must match an existing account.journal of type=bank.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>partner_id</t>
+          <t>payment_ref</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Customer or vendor display name. Odoo's import wizard resolves this to res.partner by name. Setting the partner lets Odoo derive the counterpart account automatically — this is what removes 'Set Partner' and 'Set Account' from the reconciliation widget.</t>
+          <t>Unique bank reference: UTR / NEFT / IMPS / UPI Ref ID / cheque number. Shown as the label on the statement line.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>partner_bank_id/acc_number</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Counterparty IBAN / bank account number. Sub-field path lets the Many2one to res.partner.bank resolve. Optional — leave blank if unknown.</t>
+          <t>Signed amount. Positive (+) = money in (credit). Negative (−) = money out (debit).</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="5" t="inlineStr"/>
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>partner_id</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Customer or vendor display name. base_import resolves it to res.partner by name_search. Setting the partner lets Odoo derive the counterpart account automatically — that's what removes 'Set Partner' and 'Set Account' from the Bank Matching widget.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>Why the previous template showed 'Set Partner' / 'Set Account'</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr"/>
+          <t>partner_bank_id/acc_number</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Counterparty IBAN / bank account number. Sub-field path lets the Many2one to res.partner.bank resolve. Optional — leave blank if unknown.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>partner_name</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Not a real field on account.bank.statement.line. Imported values were silently discarded, so every line ended up partner-less → 'Set Partner' button appeared. Replaced with partner_id.</t>
-        </is>
-      </c>
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>transaction_type</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>Not a real field either. Odoo derives credit vs debit from the sign of 'amount'. Removed.</t>
-        </is>
-      </c>
+          <t>Why the previous template kept showing 'Set Partner' / 'Set Account'</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>partner_bank_id (raw IBAN)</t>
+          <t>Wrong import path</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>partner_bank_id is a Many2one — importing a raw IBAN string under that column name does not resolve. Use partner_bank_id/acc_number so the import wizard maps to the bank account record.</t>
+          <t>The 'Bank journal → Import' button runs the bank-statement file parser, not base_import. That parser only auto-links partners via IBAN, and ignores partner_id even if you supply it. For UPI/UTR-only counterparties (Zepto, Swiggy, BESCOM…) it can't resolve a partner at all → 'Set Partner' button on every row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>partner_name (old column)</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>partner_name IS a real Char field on account.bank.statement.line, but it's only the raw counterparty text from the statement — it does not link to res.partner. Replaced with partner_id, which base_import resolves to a real partner record.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>transaction_type (old column)</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Not a field on account.bank.statement.line. Odoo derives credit vs debit from the sign of 'amount'. Removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>partner_bank_id (raw IBAN, old column)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>partner_bank_id is a Many2one — importing a raw IBAN string under that bare column name doesn't resolve. Use partner_bank_id/acc_number so base_import maps to the res.partner.bank record.</t>
         </is>
       </c>
     </row>
